--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/03_Segundo_Turno_Lula_vs_Flavio.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/03_Segundo_Turno_Lula_vs_Flavio.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2166,7 +2166,7 @@
         <v>46168</v>
       </c>
       <c r="B157" t="n">
-        <v>51.64855924188445</v>
+        <v>51.64855924188443</v>
       </c>
       <c r="C157" t="n">
         <v>48.35144075811557</v>
@@ -2180,7 +2180,7 @@
         <v>51.92803639942314</v>
       </c>
       <c r="C158" t="n">
-        <v>48.07196360057688</v>
+        <v>48.07196360057687</v>
       </c>
     </row>
     <row r="159">
@@ -2188,7 +2188,7 @@
         <v>46180</v>
       </c>
       <c r="B159" t="n">
-        <v>52.3871530821569</v>
+        <v>52.38715308215689</v>
       </c>
       <c r="C159" t="n">
         <v>47.61284691784311</v>
@@ -2199,7 +2199,7 @@
         <v>46181</v>
       </c>
       <c r="B160" t="n">
-        <v>52.35949466911592</v>
+        <v>52.35949466911593</v>
       </c>
       <c r="C160" t="n">
         <v>47.64050533088407</v>
@@ -2210,7 +2210,7 @@
         <v>46187</v>
       </c>
       <c r="B161" t="n">
-        <v>52.72962954991402</v>
+        <v>52.72962954991401</v>
       </c>
       <c r="C161" t="n">
         <v>47.27037045008599</v>
@@ -2235,7 +2235,7 @@
         <v>52.42375605258484</v>
       </c>
       <c r="C163" t="n">
-        <v>47.57624394741516</v>
+        <v>47.57624394741517</v>
       </c>
     </row>
     <row r="164">
@@ -2269,6 +2269,17 @@
       </c>
       <c r="C166" t="n">
         <v>47.3034771263153</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B167" t="n">
+        <v>52.50366577499383</v>
+      </c>
+      <c r="C167" t="n">
+        <v>47.49633422500615</v>
       </c>
     </row>
   </sheetData>
@@ -2282,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4012,7 +4023,7 @@
         <v>46168</v>
       </c>
       <c r="B157" t="n">
-        <v>51.32247256219033</v>
+        <v>51.32247256219031</v>
       </c>
       <c r="C157" t="n">
         <v>48.02535407842146</v>
@@ -4026,7 +4037,7 @@
         <v>51.57424419539213</v>
       </c>
       <c r="C158" t="n">
-        <v>47.71817139654587</v>
+        <v>47.71817139654586</v>
       </c>
     </row>
     <row r="159">
@@ -4034,10 +4045,10 @@
         <v>46180</v>
       </c>
       <c r="B159" t="n">
-        <v>51.99670982338623</v>
+        <v>51.99670982338622</v>
       </c>
       <c r="C159" t="n">
-        <v>47.22240365907245</v>
+        <v>47.22240365907244</v>
       </c>
     </row>
     <row r="160">
@@ -4056,7 +4067,7 @@
         <v>46187</v>
       </c>
       <c r="B161" t="n">
-        <v>52.26609149185008</v>
+        <v>52.26609149185007</v>
       </c>
       <c r="C161" t="n">
         <v>46.80683239202205</v>
@@ -4081,7 +4092,7 @@
         <v>51.7178295887664</v>
       </c>
       <c r="C163" t="n">
-        <v>46.87031748359673</v>
+        <v>46.87031748359674</v>
       </c>
     </row>
     <row r="164">
@@ -4115,6 +4126,17 @@
       </c>
       <c r="C166" t="n">
         <v>46.32981922084402</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B167" t="n">
+        <v>51.45639129958978</v>
+      </c>
+      <c r="C167" t="n">
+        <v>46.44905974960211</v>
       </c>
     </row>
   </sheetData>
@@ -4128,7 +4150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5858,7 +5880,7 @@
         <v>46168</v>
       </c>
       <c r="B157" t="n">
-        <v>51.97464592157856</v>
+        <v>51.97464592157854</v>
       </c>
       <c r="C157" t="n">
         <v>48.67752743780969</v>
@@ -5872,7 +5894,7 @@
         <v>52.28182860345414</v>
       </c>
       <c r="C158" t="n">
-        <v>48.42575580460789</v>
+        <v>48.42575580460788</v>
       </c>
     </row>
     <row r="159">
@@ -5880,10 +5902,10 @@
         <v>46180</v>
       </c>
       <c r="B159" t="n">
-        <v>52.77759634092757</v>
+        <v>52.77759634092755</v>
       </c>
       <c r="C159" t="n">
-        <v>48.00329017661378</v>
+        <v>48.00329017661377</v>
       </c>
     </row>
     <row r="160">
@@ -5891,7 +5913,7 @@
         <v>46181</v>
       </c>
       <c r="B160" t="n">
-        <v>52.75190688362565</v>
+        <v>52.75190688362566</v>
       </c>
       <c r="C160" t="n">
         <v>48.03291754539381</v>
@@ -5927,7 +5949,7 @@
         <v>53.12968251640327</v>
       </c>
       <c r="C163" t="n">
-        <v>48.2821704112336</v>
+        <v>48.28217041123361</v>
       </c>
     </row>
     <row r="164">
@@ -5961,6 +5983,17 @@
       </c>
       <c r="C166" t="n">
         <v>48.27713503178658</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B167" t="n">
+        <v>53.55094025039787</v>
+      </c>
+      <c r="C167" t="n">
+        <v>48.5436087004102</v>
       </c>
     </row>
   </sheetData>
